--- a/Lista_Precios.xlsx
+++ b/Lista_Precios.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Learning\Cotizaciones\WEB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Learning\Cotizaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3885EEF0-547E-4272-85BC-CCF4CB42F767}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1954EA5D-43EB-4659-B182-C92399144D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4CD73027-EAF4-4870-B478-8B201DB8E373}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Descripcion</t>
   </si>
@@ -104,22 +104,16 @@
     <t>Pasadía Estudiantes</t>
   </si>
   <si>
+    <t>Cerveza</t>
+  </si>
+  <si>
+    <t>Agua</t>
+  </si>
+  <si>
     <t>Termo Café</t>
   </si>
   <si>
-    <t>Cerveza</t>
-  </si>
-  <si>
-    <t>Agua</t>
-  </si>
-  <si>
     <t>Descuento</t>
-  </si>
-  <si>
-    <t>Entradas</t>
-  </si>
-  <si>
-    <t>Postre</t>
   </si>
 </sst>
 </file>
@@ -221,7 +215,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -229,9 +223,8 @@
     <xf numFmtId="164" fontId="0" fillId="3" borderId="2" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -568,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEBD858B-891B-46F6-A714-7DF097C8024F}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.5546875" bestFit="1" customWidth="1"/>
@@ -737,7 +730,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B21" s="4">
         <v>15000</v>
@@ -745,7 +738,7 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22" s="6">
         <v>5000</v>
@@ -753,7 +746,7 @@
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" s="4">
         <v>3500</v>
@@ -765,22 +758,6 @@
       </c>
       <c r="B24" s="8">
         <v>-5000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="8">
-        <v>8500</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="8">
-        <v>5000</v>
       </c>
     </row>
   </sheetData>
